--- a/AED.xlsx
+++ b/AED.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,6 +57,10 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -99,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -114,6 +118,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -542,7 +547,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>サンプル町1-1</t>
+          <t>大分県日田市サンプル町1-1</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
@@ -580,7 +585,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>サンプル町2-3</t>
+          <t>大分県日田市サンプル町2-3</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
@@ -614,7 +619,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>サンプル町3-5</t>
+          <t>大分県日田市サンプル町3-5</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -648,7 +653,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>サンプル町4-2</t>
+          <t>大分県日田市サンプル町4-2</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -686,7 +691,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>サンプル駅前1</t>
+          <t>大分県日田市サンプル駅前1</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -720,7 +725,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>サンプル町5-7</t>
+          <t>大分県日田市サンプル町5-7</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -758,7 +763,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>サンプル町6-1</t>
+          <t>大分県日田市サンプル町6-1</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
@@ -792,7 +797,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>サンプル町7-4</t>
+          <t>大分県日田市サンプル町7-4</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
@@ -829,7 +834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -838,7 +843,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>AED.xlsx の編集方法</t>
+          <t>日田市AEDナビ ― AED.xlsx の編集方法</t>
         </is>
       </c>
     </row>
@@ -853,76 +858,83 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>・1行目は見出し行です。列の順番は自由ですが、見出し名は変更しないでください。</t>
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>・このアプリは大分県日田市専用です。日田市内のAEDの座標（緯度 約33.1〜33.6 / 経度 約130.6〜131.3）を入力してください。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>・「施設名」「緯度」「経度」は必須です。緯度・経度が空欄または数値でない行は読み込まれません。</t>
+          <t>・1行目は見出し行です。列の順番は自由ですが、見出し名は変更しないでください。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>・緯度・経度は十進法（例: 33.321300 / 130.941600）で入力します。</t>
+          <t>・「施設名」「緯度」「経度」は必須です。緯度・経度が空欄または数値でない行は読み込まれません。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>・「利用可能時間」に「24時間」を含む行は、アプリの「24時間使えるAEDのみ」で絞り込まれます。</t>
+          <t>・緯度・経度は十進法（例: 33.321300 / 130.941600）で入力します。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
+          <t>・「利用可能時間」に「24時間」を含む行は、アプリの「24時間使えるAEDのみ」で絞り込まれます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
           <t>・「住所」「設置場所」「利用可能時間」「電話番号」「備考」は任意です。</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr"/>
-    </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>【重要】AEDシートの8行はすべてダミーデータです。実際のAED情報に置き換えてから公開してください。</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr"/>
-    </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>見出しの別名（自動認識）</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>施設名: 施設名 / 名称 / 名前　　緯度: 緯度 / lat / latitude　　経度: 経度 / lng / lon / longitude</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>住所: 住所 / 所在地　　設置場所: 設置場所 / 設置位置　　利用可能時間: 利用可能時間 / 利用時間</t>
+          <t>施設名: 施設名 / 名称 / 名前　　緯度: 緯度 / lat / latitude　　経度: 経度 / lng / lon / longitude</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>住所: 住所 / 所在地　　設置場所: 設置場所 / 設置位置　　利用可能時間: 利用可能時間 / 利用時間</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>電話番号: 電話番号 / 電話 / tel　　備考: 備考 / メモ</t>
         </is>
